--- a/final_data_pipeline/output/311514_elec_options.xlsx
+++ b/final_data_pipeline/output/311514_elec_options.xlsx
@@ -795,7 +795,7 @@
         <v>72</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -890,7 +890,7 @@
         <v>72</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -985,7 +985,7 @@
         <v>72</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1080,7 +1080,7 @@
         <v>72</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1175,7 +1175,7 @@
         <v>72</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1270,7 +1270,7 @@
         <v>72</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1365,7 +1365,7 @@
         <v>72</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1460,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1555,7 +1555,7 @@
         <v>72</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1650,7 +1650,7 @@
         <v>72</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1745,7 +1745,7 @@
         <v>72</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1840,7 +1840,7 @@
         <v>72</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -1935,7 +1935,7 @@
         <v>72</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2030,7 +2030,7 @@
         <v>72</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2125,7 +2125,7 @@
         <v>72</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -4120,7 +4120,7 @@
         <v>72</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -4215,7 +4215,7 @@
         <v>72</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE38">
         <v>8000</v>
@@ -4310,7 +4310,7 @@
         <v>72</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE39">
         <v>8000</v>
@@ -4405,7 +4405,7 @@
         <v>72</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE40">
         <v>8000</v>
@@ -4500,7 +4500,7 @@
         <v>72</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE41">
         <v>8000</v>
@@ -4595,7 +4595,7 @@
         <v>72</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE42">
         <v>8000</v>
@@ -4690,7 +4690,7 @@
         <v>72</v>
       </c>
       <c r="AD43">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE43">
         <v>8000</v>
@@ -4785,7 +4785,7 @@
         <v>72</v>
       </c>
       <c r="AD44">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE44">
         <v>8000</v>
@@ -4880,7 +4880,7 @@
         <v>72</v>
       </c>
       <c r="AD45">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE45">
         <v>8000</v>
@@ -4975,7 +4975,7 @@
         <v>72</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -5545,7 +5545,7 @@
         <v>72</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5640,7 +5640,7 @@
         <v>72</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5735,7 +5735,7 @@
         <v>72</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -5830,7 +5830,7 @@
         <v>72</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -5925,7 +5925,7 @@
         <v>72</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -6020,7 +6020,7 @@
         <v>72</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -6115,7 +6115,7 @@
         <v>72</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6210,7 +6210,7 @@
         <v>72</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6305,7 +6305,7 @@
         <v>72</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6400,7 +6400,7 @@
         <v>72</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -6495,7 +6495,7 @@
         <v>72</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6590,7 +6590,7 @@
         <v>72</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -6685,7 +6685,7 @@
         <v>72</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -6780,7 +6780,7 @@
         <v>72</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -6875,7 +6875,7 @@
         <v>72</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -7920,7 +7920,7 @@
         <v>72</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE77">
         <v>8000</v>
@@ -8015,7 +8015,7 @@
         <v>72</v>
       </c>
       <c r="AD78">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE78">
         <v>8000</v>
@@ -8110,7 +8110,7 @@
         <v>72</v>
       </c>
       <c r="AD79">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE79">
         <v>8000</v>
@@ -8205,7 +8205,7 @@
         <v>72</v>
       </c>
       <c r="AD80">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE80">
         <v>8000</v>
@@ -8300,7 +8300,7 @@
         <v>72</v>
       </c>
       <c r="AD81">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE81">
         <v>8000</v>
@@ -8870,7 +8870,7 @@
         <v>72</v>
       </c>
       <c r="AD87">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE87">
         <v>8000</v>
@@ -8965,7 +8965,7 @@
         <v>72</v>
       </c>
       <c r="AD88">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE88">
         <v>8000</v>
@@ -9060,7 +9060,7 @@
         <v>72</v>
       </c>
       <c r="AD89">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE89">
         <v>8000</v>
@@ -9155,7 +9155,7 @@
         <v>72</v>
       </c>
       <c r="AD90">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE90">
         <v>8000</v>
@@ -9250,7 +9250,7 @@
         <v>72</v>
       </c>
       <c r="AD91">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE91">
         <v>8000</v>
